--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-rtos-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-rtos-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Scheduler là hạt nhân của RTOS, chịu trách nhiệm quản lý trạng thái của các task và chuyển đổi quyền thực thi CPU dựa trên thuật toán lập lịch (thường là Preemptive scheduling dựa trên priority).</v>
       </c>
       <c r="F2" t="str">
+        <v>Mã hóa toàn bộ mã nguồn của file chạy binary trước khi nạp vào chip Flash — mã hóa tệp tin nạp</v>
+      </c>
+      <c r="G2" t="str">
         <v>Quyết định task nào có độ ưu tiên cao nhất đang sẵn sàng sẽ được cấp quyền CPU để chạy tiếp theo — bộ điều phối luồng chạy</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Tự động giải phóng dung lượng bộ nhớ RAM của vi điều khiển khi bị đầy — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="H2" t="str">
         <v>Đọc tín hiệu điện áp từ chân ADC và chuyển đổi sang dạng số nguyên — đọc tín hiệu ngoại vi</v>
       </c>
       <c r="I2" t="str">
-        <v>Mã hóa toàn bộ mã nguồn của file chạy binary trước khi nạp vào chip Flash — mã hóa tệp tin nạp</v>
+        <v>Tự động giải phóng dung lượng bộ nhớ RAM của vi điều khiển khi bị đầy — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Task ở trạng thái Blocked không tranh chấp CPU. Nó chỉ quay lại trạng thái Ready khi sự kiện nó chờ đợi được đáp ứng (ví dụ: hết thời gian delay hoặc nhận được semaphore).</v>
       </c>
       <c r="F3" t="str">
+        <v>Task đang trực tiếp sử dụng CPU để tính toán các thuật toán toán học — đang chạy thực tế</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Task đã bị xóa vĩnh viễn khỏi bộ nhớ của vi điều khiển và không thể gọi lại được — bị xóa khỏi RAM</v>
+      </c>
+      <c r="H3" t="str">
         <v>Task đang dừng chạy để đợi một sự kiện hoặc tài nguyên xảy ra (như Semaphore, Delay, Queue) — đợi sự kiện tài nguyên</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Task đang trực tiếp sử dụng CPU để tính toán các thuật toán toán học — đang chạy thực tế</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Task đã bị xóa vĩnh viễn khỏi bộ nhớ của vi điều khiển và không thể gọi lại được — bị xóa khỏi RAM</v>
       </c>
       <c r="I3" t="str">
         <v>Task đang bị lỗi cú pháp lập trình khiến hệ điều hành không biên dịch được — lỗi cú pháp mã nguồn</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>Semaphore (như Binary Semaphore) — cơ chế phát tín hiệu đồng bộ hóa gọn nhẹ — phát tín hiệu đồng bộ</v>
       </c>
       <c r="G4" t="str">
-        <v>Mutex (Mutual Exclusion) — cơ chế khóa độc quyền có hỗ trợ kế thừa độ ưu tiên — khóa loại trừ tương hỗ</v>
+        <v>Dynamic Memory Allocation (Cấp phát động malloc/free) — cấp phát động bộ nhớ heap</v>
       </c>
       <c r="H4" t="str">
         <v>Global Variable (Biến toàn cục thông thường) không khai báo volatile — biến thường không an toàn ngắt</v>
       </c>
       <c r="I4" t="str">
-        <v>Dynamic Memory Allocation (Cấp phát động malloc/free) — cấp phát động bộ nhớ heap</v>
+        <v>Mutex (Mutual Exclusion) — cơ chế khóa độc quyền có hỗ trợ kế thừa độ ưu tiên — khóa loại trừ tương hỗ</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -556,7 +556,7 @@
         <v>Vòng lặp trễ (busy waiting) làm lãng phí năng lượng và tài nguyên CPU. `vTaskDelay()` cho phép RTOS chuyển ngữ cảnh sang task Ready khác, tối ưu hóa đa nhiệm.</v>
       </c>
       <c r="F5" t="str">
-        <v>Vì `vTaskDelay()` đưa task hiện tại vào trạng thái Blocked để nhường CPU cho các task khác chạy; vòng lặp trễ chiếm dụng 100% CPU vô ích — giải phóng CPU cho task khác</v>
+        <v>Vì hàm này chỉ chạy được trên các dòng vi điều khiển 8-bit giá rẻ — giới hạn phần cứng chip</v>
       </c>
       <c r="G5" t="str">
         <v>Vì `vTaskDelay()` tự động khóa toàn bộ các ngắt toàn cục của vi điều khiển — khóa ngắt toàn cục</v>
@@ -565,10 +565,10 @@
         <v>Vì `vTaskDelay()` giúp vi điều khiển chạy nhanh gấp 10 lần so với bình thường — tăng tốc độ chip</v>
       </c>
       <c r="I5" t="str">
-        <v>Vì hàm này chỉ chạy được trên các dòng vi điều khiển 8-bit giá rẻ — giới hạn phần cứng chip</v>
+        <v>Vì `vTaskDelay()` đưa task hiện tại vào trạng thái Blocked để nhường CPU cho các task khác chạy; vòng lặp trễ chiếm dụng 100% CPU vô ích — giải phóng CPU cho task khác</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -594,10 +594,10 @@
         <v>Độ ưu tiên của task đó so với các task khác trong hệ thống — độ ưu tiên của task</v>
       </c>
       <c r="H6" t="str">
+        <v>Số lượng các biến toàn cục mà task được phép truy cập trong chương trình — giới hạn truy cập biến</v>
+      </c>
+      <c r="I6" t="str">
         <v>Thời gian tối đa task được phép chiếm dụng CPU trong một chu kỳ lập lịch — khung thời gian chạy</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Số lượng các biến toàn cục mà task được phép truy cập trong chương trình — giới hạn truy cập biến</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -620,19 +620,19 @@
         <v>Message Queue cho phép gửi các bản tin (struct, con trỏ dữ liệu) giữa các luồng chạy độc lập một cách an toàn, tránh lỗi xung đột tranh chấp bộ nhớ (Race Condition).</v>
       </c>
       <c r="F7" t="str">
+        <v>Lưu trữ mã nguồn code dưới dạng tệp tin nén zip trên bộ nhớ Flash của chip — lưu trữ mã nguồn</v>
+      </c>
+      <c r="G7" t="str">
         <v>Truyền và trao đổi dữ liệu an toàn giữa các tasks hoặc giữa ISR và tasks theo cơ chế hàng đợi FIFO — truyền dữ liệu đa nhiệm an toàn</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Tự động gửi tin nhắn SMS báo cáo trạng thái của chip về điện thoại của lập trình viên — gửi tin nhắn SMS</v>
       </c>
       <c r="H7" t="str">
         <v>Đo lường thời gian trễ của đường truyền internet kết nối vào vi điều khiển — đo lường độ trễ mạng</v>
       </c>
       <c r="I7" t="str">
-        <v>Lưu trữ mã nguồn code dưới dạng tệp tin nén zip trên bộ nhớ Flash của chip — lưu trữ mã nguồn</v>
+        <v>Tự động gửi tin nhắn SMS báo cáo trạng thái của chip về điện thoại của lập trình viên — gửi tin nhắn SMS</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Context Switching bao gồm việc lưu các thanh ghi CPU của task cũ vào stack của nó, cập nhật con trỏ stack, và nạp lại các thanh ghi CPU từ stack của task mới để bắt đầu thực thi.</v>
       </c>
       <c r="F8" t="str">
-        <v>Quá trình lưu lại trạng thái CPU của task đang chạy và khôi phục trạng thái CPU của task tiếp theo để thực thi — chuyển đổi trạng thái CPU</v>
+        <v>Quá trình thay đổi ngôn ngữ lập trình của dự án từ C sang C++ — thay đổi ngôn ngữ code</v>
       </c>
       <c r="G8" t="str">
         <v>Quá trình nạp lại firmware mới cho vi điều khiển thông qua cổng nạp SWD — nạp lại firmware mới</v>
       </c>
       <c r="H8" t="str">
+        <v>Quá trình lưu lại trạng thái CPU của task đang chạy và khôi phục trạng thái CPU của task tiếp theo để thực thi — chuyển đổi trạng thái CPU</v>
+      </c>
+      <c r="I8" t="str">
         <v>Quá trình chuyển đổi tín hiệu từ dạng tương tự (Analog) sang dạng số (Digital) — chuyển đổi tín hiệu ADC</v>
       </c>
-      <c r="I8" t="str">
-        <v>Quá trình thay đổi ngôn ngữ lập trình của dự án từ C sang C++ — thay đổi ngôn ngữ code</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Sau khi đã khai báo các task, queue, semaphore trong hàm `main()`, ta gọi `vTaskStartScheduler()` để trao quyền điều phối CPU hoàn toàn cho RTOS.</v>
       </c>
       <c r="F9" t="str">
+        <v>vTaskDelay() — dùng để đưa task vào trạng thái delay tạm thời — trì hoãn task</v>
+      </c>
+      <c r="G9" t="str">
         <v>vTaskStartScheduler() — bắt đầu khởi chạy hệ điều hành thời gian thực — khởi chạy scheduler</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>xTaskCreate() — dùng để khai báo và tạo một task mới trong hệ thống — tạo task mới</v>
-      </c>
-      <c r="H9" t="str">
-        <v>vTaskDelay() — dùng để đưa task vào trạng thái delay tạm thời — trì hoãn task</v>
       </c>
       <c r="I9" t="str">
         <v>taskYIELD() — dùng để nhường quyền CPU chủ động cho task khác có cùng priority — nhường quyền CPU</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>RTOS ưu tiên tính thời gian thực (Real-time). Lập lịch dựa trên độ ưu tiên (Priority-based preemptive) đảm bảo task khẩn cấp (như bung túi khí ô tô) được thực thi ngay lập tức khi kích hoạt, không bị delay ngẫu nhiên như hệ điều hành thông thường.</v>
       </c>
       <c r="F10" t="str">
-        <v>RTOS đảm bảo tính xác định về mặt thời gian (Deterministic), các task quan trọng luôn được xử lý trong một khoảng thời gian cam kết cố định — tính xác định thời gian</v>
+        <v>RTOS chỉ hỗ trợ chạy đơn luồng (Single-thread) chứ không hỗ trợ đa nhiệm — giới hạn đơn nhiệm</v>
       </c>
       <c r="G10" t="str">
-        <v>RTOS chỉ hỗ trợ chạy đơn luồng (Single-thread) chứ không hỗ trợ đa nhiệm — giới hạn đơn nhiệm</v>
+        <v>RTOS tự động kết nối Wi-Fi và tải firmware mới về cập nhật không cần lập trình viên — tự động cập nhật</v>
       </c>
       <c r="H10" t="str">
         <v>RTOS yêu cầu phần cứng máy tính cực kỳ mạnh mẽ với dung lượng RAM trên 8GB — yêu cầu phần cứng lớn</v>
       </c>
       <c r="I10" t="str">
-        <v>RTOS tự động kết nối Wi-Fi và tải firmware mới về cập nhật không cần lập trình viên — tự động cập nhật</v>
+        <v>RTOS đảm bảo tính xác định về mặt thời gian (Deterministic), các task quan trọng luôn được xử lý trong một khoảng thời gian cam kết cố định — tính xác định thời gian</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>Khi task có độ ưu tiên thấp không bao giờ được cấp quyền chạy vì CPU liên tục bận xử lý các task khác có độ ưu tiên cao hơn — đói CPU do lệch độ ưu tiên</v>
       </c>
       <c r="G11" t="str">
-        <v>Khi nguồn điện cấp cho vi điều khiển bị sụt áp xuống dưới mức 3.3V — sụt áp nguồn điện chip</v>
+        <v>Khi task bị chặn truy cập vào các biến toàn cục khai báo static — khóa truy cập biến static</v>
       </c>
       <c r="H11" t="str">
         <v>Khi vùng nhớ Stack của task bị cạn kiệt do gọi đệ quy vô hạn — tràn stack bộ nhớ</v>
       </c>
       <c r="I11" t="str">
-        <v>Khi task bị chặn truy cập vào các biến toàn cục khai báo static — khóa truy cập biến static</v>
+        <v>Khi nguồn điện cấp cho vi điều khiển bị sụt áp xuống dưới mức 3.3V — sụt áp nguồn điện chip</v>
       </c>
       <c r="J11">
         <v>1</v>
